--- a/data/trending_integrated_20261022_13.xlsx
+++ b/data/trending_integrated_20261022_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3615</v>
+        <v>3620</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.99%</t>
+          <t>'+17.15%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G2" t="n">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>68308415936</v>
+        <v>69230799524</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -622,7 +622,7 @@
         <v>-28000</v>
       </c>
       <c r="S2" t="n">
-        <v>150000</v>
+        <v>195000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55300</v>
+        <v>55400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.93%</t>
+          <t>'+16.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F3" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G3" t="n">
-        <v>1254</v>
+        <v>1284</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>525369995550</v>
+        <v>528609413950</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -714,20 +714,20 @@
         <v>1412000</v>
       </c>
       <c r="S3" t="n">
-        <v>410000</v>
+        <v>520000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 역대급 실적 발표 및 자사주 취득 동시 발표. MSCI 편입 예상과 함께 주가 상승 기대감 고조.</t>
+          <t>삼성E&amp;A, 어닝 서프라이즈 및 자사주 취득 공시 발표. MSCI 편입 예상 등 긍정적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '자사주 취득', 'MSCI 편입']</t>
+          <t>['어닝 서프라이즈', '자사주 취득', 'MSCI 편입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7360</v>
+        <v>7390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.51%</t>
+          <t>'+10.96%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
         <v>25</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8638039520</v>
+        <v>8661662340</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -803,7 +803,7 @@
         <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>38000</v>
+        <v>41000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1699</v>
+        <v>1706</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.53%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>20634410409</v>
+        <v>20778305800</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14700</v>
+        <v>17930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.13</v>
+        <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>238</v>
+        <v>124</v>
       </c>
       <c r="H6" t="n">
-        <v>9.949999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14770</v>
+        <v>17920</v>
       </c>
       <c r="K6" t="n">
-        <v>14770</v>
+        <v>19180</v>
       </c>
       <c r="L6" t="n">
-        <v>15290</v>
+        <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>14610</v>
+        <v>17690</v>
       </c>
       <c r="N6" t="n">
-        <v>9.82</v>
+        <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>34132208755</v>
+        <v>70848256890</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>-69000</v>
+        <v>-37000</v>
       </c>
       <c r="S6" t="n">
-        <v>-22000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인 및 연기금 순매수세 유입에도 건설주 전반의 낮은 상승률에 대한 불만 표출. 대차해지 운동 촉구.</t>
+          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 매수', '건설주', '대차해지']</t>
+          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17740</v>
+        <v>14760</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.00%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.32</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="H7" t="n">
-        <v>3.29</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17920</v>
+        <v>14770</v>
       </c>
       <c r="K7" t="n">
-        <v>19180</v>
+        <v>14770</v>
       </c>
       <c r="L7" t="n">
-        <v>20150</v>
+        <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>17690</v>
+        <v>14610</v>
       </c>
       <c r="N7" t="n">
-        <v>3.61</v>
+        <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>70278091380</v>
+        <v>34633563430</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>6320</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-2000</v>
+        <v>15000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-63000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전 세계 보안 이슈 확산 속 라온시큐어 보안 관련 뉴스 주목. 다만, 주가 변동성과 외국인 단타 매매에 대한 경계심도 존재.</t>
+          <t>외국인 및 연기금 순매수세 유입에도 건설주 전반의 낮은 상승률에 대한 불만 표출. 대차해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안 이슈', 'PHP 취약점', '외국인 단타']</t>
+          <t>['외국인 매수', '건설주', '대차해지']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7200</v>
+        <v>7190</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>127</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="H8" t="n">
         <v>25.47</v>
@@ -1162,7 +1162,7 @@
         <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>10003263710</v>
+        <v>10163320530</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1171,23 +1171,23 @@
         <v>7170</v>
       </c>
       <c r="R8" t="n">
-        <v>-180000</v>
+        <v>-148000</v>
       </c>
       <c r="S8" t="n">
-        <v>-31000</v>
+        <v>-69000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>LG디스플레이, 부진한 실적 발표 후 주가 하락. 30년 최저가 근접 및 투자자들의 실망감 표출.</t>
+          <t>LG디스플레이, 3분기 흑자 전환에도 불구하고 주가 부진. 높은 투자 대비 낮은 주가 흐름에 대한 불만.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업손실', '주가 하락', '최저가']</t>
+          <t>['흑자 전환', '주가 부진', '투자 대비 성과']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G9" t="n">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>10392831700</v>
+        <v>10717543800</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1263,7 +1263,7 @@
         <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>18000</v>
+        <v>46000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13940</v>
+        <v>13930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.33</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="H10" t="n">
         <v>3.48</v>
@@ -1340,13 +1340,13 @@
         <v>14830</v>
       </c>
       <c r="M10" t="n">
-        <v>13890</v>
+        <v>13790</v>
       </c>
       <c r="N10" t="n">
         <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>91641878980</v>
+        <v>94885645395</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1358,7 +1358,7 @@
         <v>-389000</v>
       </c>
       <c r="S10" t="n">
-        <v>16000</v>
+        <v>-3000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14490</v>
+        <v>14500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1.2</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H11" t="n">
         <v>1.2</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>74972089765</v>
+        <v>75932959400</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1447,23 +1447,23 @@
         <v>12030</v>
       </c>
       <c r="R11" t="n">
-        <v>-54000</v>
+        <v>-51000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대만 반도체 파업 및 마이크론 관련 뉴스에 따른 주가 변동성 확대. 신규 상장주 수급 집중 우려.</t>
+          <t>멜콘, 조선일보 보도 및 반도체 관련 이슈 언급. 보호예수 해제 및 수급 요인에 따른 주가 변동성 관찰.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체 파업', '마이크론', '변동성']</t>
+          <t>['반도체 이슈', '보호예수 해제', '수급 변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214500</v>
+        <v>9820</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
-        <v>545</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>1480</v>
+        <v>342</v>
       </c>
       <c r="H12" t="n">
-        <v>46.14</v>
+        <v>5.87</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>223500</v>
+        <v>10190</v>
       </c>
       <c r="K12" t="n">
-        <v>221500</v>
+        <v>10110</v>
       </c>
       <c r="L12" t="n">
-        <v>226000</v>
+        <v>10180</v>
       </c>
       <c r="M12" t="n">
-        <v>214000</v>
+        <v>9620</v>
       </c>
       <c r="N12" t="n">
-        <v>46.08</v>
+        <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>1445408127750</v>
+        <v>14647107510</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>14940</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>5390</v>
       </c>
       <c r="R12" t="n">
-        <v>-677000</v>
+        <v>-56000</v>
       </c>
       <c r="S12" t="n">
-        <v>-254000</v>
+        <v>23000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국가 시스템 문제와 정치적 요인에 따른 주가 하락 분석. 개인 매도세와 외국인 매도세 관찰.</t>
+          <t>명신산업, 테슬라 실적 호조에도 불구하고 주가 하락. 투자자들의 공매도 및 세력 이탈 의혹 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국가 시스템', '주가 하락', '개인 매도']</t>
+          <t>['테슬라 실적', '공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9730</v>
+        <v>214500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.51%</t>
+          <t>'-4.03%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>542</v>
       </c>
       <c r="G13" t="n">
-        <v>339</v>
+        <v>1496</v>
       </c>
       <c r="H13" t="n">
-        <v>5.87</v>
+        <v>46.14</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10190</v>
+        <v>223500</v>
       </c>
       <c r="K13" t="n">
-        <v>10110</v>
+        <v>221500</v>
       </c>
       <c r="L13" t="n">
-        <v>10180</v>
+        <v>226000</v>
       </c>
       <c r="M13" t="n">
-        <v>9620</v>
+        <v>213500</v>
       </c>
       <c r="N13" t="n">
-        <v>5.34</v>
+        <v>46.08</v>
       </c>
       <c r="O13" t="n">
-        <v>14383886110</v>
+        <v>1486870612500</v>
       </c>
       <c r="P13" t="n">
-        <v>14940</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>5390</v>
+        <v>94500</v>
       </c>
       <c r="R13" t="n">
-        <v>-32000</v>
+        <v>-1004000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-549000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>테슬라 실적 및 스페이스X 관련 뉴스와 연동된 주가 움직임 관찰. 개인 투자자들의 혼조세와 공매도 우려 제기.</t>
+          <t>삼성전자, 전반적인 국가 시스템 및 정치적 상황에 대한 불만 표출. 주가 하락에 대한 분석 및 개인 투자자들의 매도세 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['주가 하락', '국가 시스템', '개인 매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1233000</v>
+        <v>1232000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.71%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="G14" t="n">
-        <v>1542</v>
+        <v>1467</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1708,13 +1708,13 @@
         <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>1229000</v>
+        <v>1228000</v>
       </c>
       <c r="N14" t="n">
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>1726122622500</v>
+        <v>1766795117000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1723,14 +1723,14 @@
         <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-55000</v>
+        <v>-62000</v>
       </c>
       <c r="S14" t="n">
-        <v>-6000</v>
+        <v>-88000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물린 SK하이닉스 주가 하락세. 최태원 회장의 '우상향' 발언과 외국인 매도세에 대한 의문 제기.</t>
+          <t>SK하이닉스, 주가 하락에 대한 정치적 이슈 연관성 언급. 최태원 회장의 주가 전망 발언 및 공매도 관련 논란.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '외국인 매도', '솔리다임']</t>
+          <t>['주가 하락', '정치적 이슈', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10000</v>
+        <v>10050</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-10.23%</t>
+          <t>'-9.78%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F15" t="n">
         <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>56274679195</v>
+        <v>56904750360</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1818,20 +1818,20 @@
         <v>-177000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 및 NXT 시장 관련 기대감 있었으나 급락. 예상치 못한 조정과 ESS 마진율 불확실성 등으로 투자 심리 위축.</t>
+          <t>HT로보틱스, 급격한 주가 하락 후 조정 국면. 투자 심리 위축 및 ESS 마진율 불확실성 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', 'NXT 시장', 'ESS 마진율']</t>
+          <t>['주가 하락', '조정 국면', 'ESS 마진율']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_13.xlsx
+++ b/data/trending_integrated_20261022_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3620</v>
+        <v>3610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.15%</t>
+          <t>'+16.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F2" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G2" t="n">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>69230799524</v>
+        <v>69881476331</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -619,23 +619,23 @@
         <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>-28000</v>
+        <v>-246000</v>
       </c>
       <c r="S2" t="n">
         <v>195000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빅텍, 김정은 신변 이상설 및 전쟁 가능성 대두로 인한 급등세. 과거 급등 사례 언급하며 추가 상승 기대감 표출. 단타 매매 심리 작용.</t>
+          <t>김정은 위원장 신변 이상설 및 사망설이 제기되며 급등세를 보였고, 전쟁 가능성 대두 및 관련 뉴스가 주가 상승의 주요 요인으로 작용함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은 신변이상설', '전쟁 가능성', '단기 급등']</t>
+          <t>['김정은', '신변이상설']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55400</v>
+        <v>55200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.14%</t>
+          <t>'+15.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F3" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G3" t="n">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>528609413950</v>
+        <v>533287962000</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8661662340</v>
+        <v>8730638000</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>루미아 인수 관련 로봇 기술 개발 기대감 고조. 현대차 파트너십 및 신규 기술 양산 가능성. 목표가 상향 제시.</t>
+          <t>자회사 루미아의 현대차 파트너십 및 로봇 촉각 센서 개발 관련 뉴스가 연이어 보도되며, 사명 변경 가능성 및 50배 상승 기대감이 주가를 견인함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아인수', '로봇기술', '촉각센서']</t>
+          <t>['루미아', '촉각센서']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1706</v>
+        <v>1719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+6.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>20778305800</v>
+        <v>21312061451</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -895,7 +895,7 @@
         <v>1115</v>
       </c>
       <c r="R5" t="n">
-        <v>126000</v>
+        <v>-71000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17930</v>
+        <v>18000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>70848256890</v>
+        <v>71174231850</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14760</v>
+        <v>14740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F7" t="n">
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>34633563430</v>
+        <v>35132289100</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1130,13 +1130,13 @@
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="H8" t="n">
         <v>25.47</v>
@@ -1162,7 +1162,7 @@
         <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>10163320530</v>
+        <v>10469414920</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>LG디스플레이, 3분기 흑자 전환에도 불구하고 주가 부진. 높은 투자 대비 낮은 주가 흐름에 대한 불만.</t>
+          <t>3분기 실적 발표 후 주가 하락이 예상되었으나, 실제 실적이 긍정적으로 발표되며 주가 반등에 대한 기대감이 형성되나, 여전히 부정적인 시장 분위기가 감지됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['흑자 전환', '주가 부진', '투자 대비 성과']</t>
+          <t>['실적', '매출']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F9" t="n">
         <v>92</v>
       </c>
       <c r="G9" t="n">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>10717543800</v>
+        <v>10977121650</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13930</v>
+        <v>9900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F10" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>472</v>
+        <v>346</v>
       </c>
       <c r="H10" t="n">
-        <v>3.48</v>
+        <v>5.87</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14310</v>
+        <v>10190</v>
       </c>
       <c r="K10" t="n">
-        <v>14180</v>
+        <v>10110</v>
       </c>
       <c r="L10" t="n">
-        <v>14830</v>
+        <v>10180</v>
       </c>
       <c r="M10" t="n">
-        <v>13790</v>
+        <v>9620</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>94885645395</v>
+        <v>15191747720</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>14940</v>
       </c>
       <c r="Q10" t="n">
-        <v>1640</v>
+        <v>5390</v>
       </c>
       <c r="R10" t="n">
-        <v>-389000</v>
+        <v>-56000</v>
       </c>
       <c r="S10" t="n">
-        <v>-3000</v>
+        <v>23000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
+          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스가 언급되었으나, 전반적인 코스피/코스닥 하락장 속에서 개인 투자자들의 매도세와 공매도 관련 언급이 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['테슬라', '스페이스X']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14500</v>
+        <v>13810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.20%</t>
+          <t>'-3.49%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>0.33</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
-        <v>170</v>
+        <v>473</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>3.48</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14980</v>
+        <v>14310</v>
       </c>
       <c r="K11" t="n">
-        <v>14460</v>
+        <v>14180</v>
       </c>
       <c r="L11" t="n">
-        <v>16140</v>
+        <v>14830</v>
       </c>
       <c r="M11" t="n">
-        <v>13550</v>
+        <v>13790</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>75932959400</v>
+        <v>96017000860</v>
       </c>
       <c r="P11" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>12030</v>
+        <v>1640</v>
       </c>
       <c r="R11" t="n">
-        <v>-51000</v>
+        <v>-506000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>멜콘, 조선일보 보도 및 반도체 관련 이슈 언급. 보호예수 해제 및 수급 요인에 따른 주가 변동성 관찰.</t>
+          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체 이슈', '보호예수 해제', '수급 변동성']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9820</v>
+        <v>214250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-4.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>546</v>
       </c>
       <c r="G12" t="n">
-        <v>342</v>
+        <v>1610</v>
       </c>
       <c r="H12" t="n">
-        <v>5.87</v>
+        <v>46.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10190</v>
+        <v>223500</v>
       </c>
       <c r="K12" t="n">
-        <v>10110</v>
+        <v>221500</v>
       </c>
       <c r="L12" t="n">
-        <v>10180</v>
+        <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>9620</v>
+        <v>213500</v>
       </c>
       <c r="N12" t="n">
-        <v>5.34</v>
+        <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>14647107510</v>
+        <v>1525478226750</v>
       </c>
       <c r="P12" t="n">
-        <v>14940</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>5390</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-56000</v>
+        <v>-1004000</v>
       </c>
       <c r="S12" t="n">
-        <v>23000</v>
+        <v>-549000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 실적 호조에도 불구하고 주가 하락. 투자자들의 공매도 및 세력 이탈 의혹 제기.</t>
+          <t>정치적 이슈에 따른 국내 증시 전반의 하락세 속에서 개인 투자자들의 매도 물량이 관찰되며, 주가 하락의 원인이 국가 시스템 붕괴 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테슬라 실적', '공매도', '주가 하락']</t>
+          <t>['국가 시스템', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>214500</v>
+        <v>14300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-4.54%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F13" t="n">
-        <v>542</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>1496</v>
+        <v>172</v>
       </c>
       <c r="H13" t="n">
-        <v>46.14</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>223500</v>
+        <v>14980</v>
       </c>
       <c r="K13" t="n">
-        <v>221500</v>
+        <v>14460</v>
       </c>
       <c r="L13" t="n">
-        <v>226000</v>
+        <v>16140</v>
       </c>
       <c r="M13" t="n">
-        <v>213500</v>
+        <v>13550</v>
       </c>
       <c r="N13" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1486870612500</v>
+        <v>76771166100</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>94500</v>
+        <v>12030</v>
       </c>
       <c r="R13" t="n">
-        <v>-1004000</v>
+        <v>-51000</v>
       </c>
       <c r="S13" t="n">
-        <v>-549000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자, 전반적인 국가 시스템 및 정치적 상황에 대한 불만 표출. 주가 하락에 대한 분석 및 개인 투자자들의 매도세 관찰.</t>
+          <t>대만 반도체 파업 및 조선일보 기사가 언급되었으나, 브릴스, 빅웨이브와의 분산 투자 및 ASML 협조 회사라는 점이 긍정적으로 부각됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 하락', '국가 시스템', '개인 매도']</t>
+          <t>['ASML', '반도체']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1232000</v>
+        <v>1218000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-5.87%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="G14" t="n">
-        <v>1467</v>
+        <v>1494</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1708,13 +1708,13 @@
         <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>1228000</v>
+        <v>1216000</v>
       </c>
       <c r="N14" t="n">
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>1766795117000</v>
+        <v>1888209520500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스, 주가 하락에 대한 정치적 이슈 연관성 언급. 최태원 회장의 주가 전망 발언 및 공매도 관련 논란.</t>
+          <t>정치적 이슈와 최태원 회장 관련 부정적 언급이 주를 이루며, 솔리다임 상장 준비와 관련된 우려가 주가 하락의 원인으로 지목됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 하락', '정치적 이슈', '공매도']</t>
+          <t>['솔리다임', '최태원']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10050</v>
+        <v>10000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.78%</t>
+          <t>'-10.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>56904750360</v>
+        <v>57356792140</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1815,23 +1815,23 @@
         <v>2270</v>
       </c>
       <c r="R15" t="n">
-        <v>-177000</v>
+        <v>-205000</v>
       </c>
       <c r="S15" t="n">
         <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>HT로보틱스, 급격한 주가 하락 후 조정 국면. 투자 심리 위축 및 ESS 마진율 불확실성 제기.</t>
+          <t>투자경고 종목 지정 가능성 및 대폭락에 대한 우려가 제기되며, ESS 마진율 불확실성 등이 주가 하락의 원인으로 언급됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 하락', '조정 국면', 'ESS 마진율']</t>
+          <t>['투자경고', 'ESS']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_13.xlsx
+++ b/data/trending_integrated_20261022_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3610</v>
+        <v>3645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.83%</t>
+          <t>'+17.96%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G2" t="n">
-        <v>517</v>
+        <v>728</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>69881476331</v>
+        <v>71127889976</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 위원장 신변 이상설 및 사망설이 제기되며 급등세를 보였고, 전쟁 가능성 대두 및 관련 뉴스가 주가 상승의 주요 요인으로 작용함.</t>
+          <t>김정은 신변 이상설로 인한 급등세, 단기 변동성 및 향후 전망에 대한 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '신변이상설']</t>
+          <t>['김정은', '신변이상설', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55200</v>
+        <v>55400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.72%</t>
+          <t>'+16.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F3" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G3" t="n">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>533287962000</v>
+        <v>539565597400</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7390</v>
+        <v>7370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.96%</t>
+          <t>'+10.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8730638000</v>
+        <v>8794585820</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1719</v>
+        <v>1702</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.77%</t>
+          <t>'+5.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>21312061451</v>
+        <v>21576118264</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 및 인수설 관련 공방. 주가 조작 의혹과 함께 혼조세를 보이는 투자 심리.</t>
+          <t>보호예수 해제 및 주가 조작 의혹 등 악재와 호재가 혼재된 상황.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수', '인수설', '주가 조작']</t>
+          <t>['보호예수', '주가조작', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,7 +946,7 @@
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
         <v>46</v>
@@ -978,7 +978,7 @@
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>71174231850</v>
+        <v>71654499310</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1038,13 +1038,13 @@
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>35132289100</v>
+        <v>35632771925</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7190</v>
+        <v>7270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.18%</t>
+          <t>'-1.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="H8" t="n">
         <v>25.47</v>
@@ -1156,19 +1156,19 @@
         <v>7340</v>
       </c>
       <c r="M8" t="n">
-        <v>7170</v>
+        <v>7120</v>
       </c>
       <c r="N8" t="n">
         <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>10469414920</v>
+        <v>12921417150</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>7170</v>
+        <v>7120</v>
       </c>
       <c r="R8" t="n">
         <v>-148000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3분기 실적 발표 후 주가 하락이 예상되었으나, 실제 실적이 긍정적으로 발표되며 주가 반등에 대한 기대감이 형성되나, 여전히 부정적인 시장 분위기가 감지됨.</t>
+          <t>3분기 실적 발표에 대한 긍정적 기대와 부정적 전망이 혼재하며 주가 흐름에 대한 혼란.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '매출']</t>
+          <t>['영업이익', '매출', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F9" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>10977121650</v>
+        <v>11242731850</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 속 기관 매수세 유입 관찰. C2 결과 및 승인 요건 미충족 가능성에 대한 논쟁.</t>
+          <t>간암 치료제 FDA 승인 기대감과 C2 확률 논쟁 속 기관 수급 및 차익실현 논의.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 치료제', '기관 매수']</t>
+          <t>['FDA', '간암', '승인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9900</v>
+        <v>9920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.65%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F10" t="n">
         <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="H10" t="n">
         <v>5.87</v>
@@ -1346,7 +1346,7 @@
         <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>15191747720</v>
+        <v>15525004430</v>
       </c>
       <c r="P10" t="n">
         <v>14940</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스가 언급되었으나, 전반적인 코스피/코스닥 하락장 속에서 개인 투자자들의 매도세와 공매도 관련 언급이 혼재.</t>
+          <t>테슬라 실적 호조 및 스페이스X 뉴스 관련 기대감과 매물 출회에 따른 혼조세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X']</t>
+          <t>['테슬라', '실적', '스페이스X']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13810</v>
+        <v>214500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.49%</t>
+          <t>'-4.03%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="G11" t="n">
-        <v>473</v>
+        <v>1651</v>
       </c>
       <c r="H11" t="n">
-        <v>3.48</v>
+        <v>46.14</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14310</v>
+        <v>223500</v>
       </c>
       <c r="K11" t="n">
-        <v>14180</v>
+        <v>221500</v>
       </c>
       <c r="L11" t="n">
-        <v>14830</v>
+        <v>226000</v>
       </c>
       <c r="M11" t="n">
-        <v>13790</v>
+        <v>213500</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>96017000860</v>
+        <v>1561341824250</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1640</v>
+        <v>94500</v>
       </c>
       <c r="R11" t="n">
-        <v>-506000</v>
+        <v>-1004000</v>
       </c>
       <c r="S11" t="n">
-        <v>-3000</v>
+        <v>-549000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
+          <t>개인 투자자들의 정치적 불만과 국내 증시 부진에 대한 부정적인 의견이 다수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['증시', '악재', '주가부양']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214250</v>
+        <v>13730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.14%</t>
+          <t>'-4.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c r="F12" t="n">
-        <v>546</v>
+        <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>1610</v>
+        <v>478</v>
       </c>
       <c r="H12" t="n">
-        <v>46.14</v>
+        <v>3.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>223500</v>
+        <v>14310</v>
       </c>
       <c r="K12" t="n">
-        <v>221500</v>
+        <v>14180</v>
       </c>
       <c r="L12" t="n">
-        <v>226000</v>
+        <v>14830</v>
       </c>
       <c r="M12" t="n">
-        <v>213500</v>
+        <v>13700</v>
       </c>
       <c r="N12" t="n">
-        <v>46.08</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1525478226750</v>
+        <v>98439011815</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>1640</v>
       </c>
       <c r="R12" t="n">
-        <v>-1004000</v>
+        <v>-506000</v>
       </c>
       <c r="S12" t="n">
-        <v>-549000</v>
+        <v>-3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈에 따른 국내 증시 전반의 하락세 속에서 개인 투자자들의 매도 물량이 관찰되며, 주가 하락의 원인이 국가 시스템 붕괴 및 공매도 관련 언급.</t>
+          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국가 시스템', '공매도']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14300</v>
+        <v>1219000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.54%</t>
+          <t>'-5.80%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>549</v>
       </c>
       <c r="G13" t="n">
-        <v>172</v>
+        <v>1527</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>48.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>1294000</v>
       </c>
       <c r="K13" t="n">
-        <v>14460</v>
+        <v>1273000</v>
       </c>
       <c r="L13" t="n">
-        <v>16140</v>
+        <v>1297000</v>
       </c>
       <c r="M13" t="n">
-        <v>13550</v>
+        <v>1214000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>76771166100</v>
+        <v>1978392966500</v>
       </c>
       <c r="P13" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>12030</v>
+        <v>468000</v>
       </c>
       <c r="R13" t="n">
-        <v>-51000</v>
+        <v>-62000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-88000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대만 반도체 파업 및 조선일보 기사가 언급되었으나, 브릴스, 빅웨이브와의 분산 투자 및 ASML 협조 회사라는 점이 긍정적으로 부각됨.</t>
+          <t>정치적 이슈와 솔리다임 상장 추진 관련 불확실성으로 인한 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['ASML', '반도체']</t>
+          <t>['솔리다임', '상장', '정치']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1218000</v>
+        <v>14060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.87%</t>
+          <t>'-6.14%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>535</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>1494</v>
+        <v>175</v>
       </c>
       <c r="H14" t="n">
-        <v>48.79</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1294000</v>
+        <v>14980</v>
       </c>
       <c r="K14" t="n">
-        <v>1273000</v>
+        <v>14460</v>
       </c>
       <c r="L14" t="n">
-        <v>1297000</v>
+        <v>16140</v>
       </c>
       <c r="M14" t="n">
-        <v>1216000</v>
+        <v>13550</v>
       </c>
       <c r="N14" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1888209520500</v>
+        <v>78147282365</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q14" t="n">
-        <v>468000</v>
+        <v>12030</v>
       </c>
       <c r="R14" t="n">
-        <v>-62000</v>
+        <v>-51000</v>
       </c>
       <c r="S14" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 최태원 회장 관련 부정적 언급이 주를 이루며, 솔리다임 상장 준비와 관련된 우려가 주가 하락의 원인으로 지목됨.</t>
+          <t>대만 반도체 파업 및 조선일보 기사가 언급되었으나, 브릴스, 빅웨이브와의 분산 투자 및 ASML 협조 회사라는 점이 긍정적으로 부각됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원']</t>
+          <t>['ASML', '반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10000</v>
+        <v>10030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-10.23%</t>
+          <t>'-9.96%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>57356792140</v>
+        <v>57744962575</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 가능성 및 대폭락에 대한 우려가 제기되며, ESS 마진율 불확실성 등이 주가 하락의 원인으로 언급됨.</t>
+          <t>ESS 마진율 불확실성 및 투자 경고 등 하락세에 대한 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투자경고', 'ESS']</t>
+          <t>['ESS', '마진율', '하락']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_13.xlsx
+++ b/data/trending_integrated_20261022_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3645</v>
+        <v>3755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.96%</t>
+          <t>'+21.52%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="F2" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>71127889976</v>
+        <v>74365470879</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55400</v>
+        <v>55200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.14%</t>
+          <t>'+15.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F3" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G3" t="n">
-        <v>1304</v>
+        <v>1316</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>539565597400</v>
+        <v>543067739850</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7370</v>
+        <v>7360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.66%</t>
+          <t>'+10.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8794585820</v>
+        <v>8873847110</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자회사 루미아의 현대차 파트너십 및 로봇 촉각 센서 개발 관련 뉴스가 연이어 보도되며, 사명 변경 가능성 및 50배 상승 기대감이 주가를 견인함.</t>
+          <t>현대차-루미아 파트너십 및 로봇 촉각 센싱 솔루션 양산. 미국 기업 루미아 인수 기반 목표 주가 상향.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아', '촉각센서']</t>
+          <t>['루미아', '촉각센서', '인수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>21576118264</v>
+        <v>21769051185</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보호예수 해제 및 주가 조작 의혹 등 악재와 호재가 혼재된 상황.</t>
+          <t>보호예수 해제 물량 및 주가 조작 의혹 제기. 특정 가격 도달 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수', '주가조작', '호재']</t>
+          <t>['보호예수', '주가조작', '매물벽']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18000</v>
+        <v>14690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'-0.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.32</v>
+        <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>124</v>
+        <v>246</v>
       </c>
       <c r="H6" t="n">
-        <v>3.29</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17920</v>
+        <v>14770</v>
       </c>
       <c r="K6" t="n">
-        <v>19180</v>
+        <v>14770</v>
       </c>
       <c r="L6" t="n">
-        <v>20150</v>
+        <v>15290</v>
       </c>
       <c r="M6" t="n">
-        <v>17690</v>
+        <v>14610</v>
       </c>
       <c r="N6" t="n">
-        <v>3.61</v>
+        <v>9.82</v>
       </c>
       <c r="O6" t="n">
-        <v>71654499310</v>
+        <v>36174939375</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-37000</v>
+        <v>15000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-63000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
+          <t>외국인 및 연기금 순매수세 유입에도 건설주 전반의 낮은 상승률에 대한 불만 표출. 대차해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
+          <t>['외국인 매수', '건설주', '대차해지']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14740</v>
+        <v>17790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>-0.32</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>245</v>
+        <v>125</v>
       </c>
       <c r="H7" t="n">
-        <v>9.949999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14770</v>
+        <v>17920</v>
       </c>
       <c r="K7" t="n">
-        <v>14770</v>
+        <v>19180</v>
       </c>
       <c r="L7" t="n">
-        <v>15290</v>
+        <v>20150</v>
       </c>
       <c r="M7" t="n">
-        <v>14610</v>
+        <v>17690</v>
       </c>
       <c r="N7" t="n">
-        <v>9.82</v>
+        <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>35632771925</v>
+        <v>72106167660</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>6320</v>
       </c>
       <c r="R7" t="n">
-        <v>15000</v>
+        <v>-37000</v>
       </c>
       <c r="S7" t="n">
-        <v>-63000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 및 연기금 순매수세 유입에도 건설주 전반의 낮은 상승률에 대한 불만 표출. 대차해지 운동 촉구.</t>
+          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인 매수', '건설주', '대차해지']</t>
+          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7270</v>
+        <v>7250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.09%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>534</v>
+        <v>587</v>
       </c>
       <c r="H8" t="n">
         <v>25.47</v>
@@ -1162,7 +1162,7 @@
         <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>12921417150</v>
+        <v>13533498150</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3분기 실적 발표에 대한 긍정적 기대와 부정적 전망이 혼재하며 주가 흐름에 대한 혼란.</t>
+          <t>영업이익 및 순이익 흑자 발표 기반 주가 상승 기대. 30년 최저가 근접 상황.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '매출', '실적']</t>
+          <t>['영업이익', '순이익', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41350</v>
+        <v>41300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F9" t="n">
         <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>11242731850</v>
+        <v>11512958250</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>간암 치료제 FDA 승인 기대감과 C2 확률 논쟁 속 기관 수급 및 차익실현 논의.</t>
+          <t>FDA 승인 기대감 속 기관 수급 확인. C2 결과 및 승인 가능성에 대한 논의.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9920</v>
+        <v>9900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.65%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>15525004430</v>
+        <v>15828221710</v>
       </c>
       <c r="P10" t="n">
         <v>14940</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>214500</v>
+        <v>213750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G11" t="n">
-        <v>1651</v>
+        <v>1617</v>
       </c>
       <c r="H11" t="n">
         <v>46.14</v>
@@ -1438,7 +1438,7 @@
         <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1561341824250</v>
+        <v>1604236940250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>개인 투자자들의 정치적 불만과 국내 증시 부진에 대한 부정적인 의견이 다수.</t>
+          <t>정치적 이슈와 무관한 증시 부진에 대한 불만 표출. 개인 투자자들의 매도세 관찰.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['증시', '악재', '주가부양']</t>
+          <t>['증시', '매도세', '시스템']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13730</v>
+        <v>13590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.05%</t>
+          <t>'-5.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.33</v>
       </c>
       <c r="E12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
         <v>478</v>
@@ -1524,13 +1524,13 @@
         <v>14830</v>
       </c>
       <c r="M12" t="n">
-        <v>13700</v>
+        <v>13580</v>
       </c>
       <c r="N12" t="n">
         <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>98439011815</v>
+        <v>102021081210</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
+          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스. 삼성전자 인수 관련 루머.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['EUV', '유리기판', 'AI광통신']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1219000</v>
+        <v>14140</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.80%</t>
+          <t>'-5.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>106</v>
       </c>
       <c r="F13" t="n">
-        <v>549</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>1527</v>
+        <v>186</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>14980</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>14460</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>16140</v>
       </c>
       <c r="M13" t="n">
-        <v>1214000</v>
+        <v>13550</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1978392966500</v>
+        <v>78734290330</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>12030</v>
       </c>
       <c r="R13" t="n">
-        <v>-62000</v>
+        <v>-51000</v>
       </c>
       <c r="S13" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 솔리다임 상장 추진 관련 불확실성으로 인한 투자 심리 악화.</t>
+          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '정치']</t>
+          <t>['반도체', 'AI', '보호예수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14060</v>
+        <v>1207500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.14%</t>
+          <t>'-6.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>543</v>
       </c>
       <c r="G14" t="n">
-        <v>175</v>
+        <v>1513</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2</v>
+        <v>48.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14980</v>
+        <v>1294000</v>
       </c>
       <c r="K14" t="n">
-        <v>14460</v>
+        <v>1273000</v>
       </c>
       <c r="L14" t="n">
-        <v>16140</v>
+        <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>13550</v>
+        <v>1204000</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>78147282365</v>
+        <v>2091217386000</v>
       </c>
       <c r="P14" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>12030</v>
+        <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-51000</v>
+        <v>-62000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-88000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대만 반도체 파업 및 조선일보 기사가 언급되었으나, 브릴스, 빅웨이브와의 분산 투자 및 ASML 협조 회사라는 점이 긍정적으로 부각됨.</t>
+          <t>정치적 이슈와 관련된 부정적 언급 및 주가 부진에 대한 불만. 거래 정지 및 분할 상장 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['ASML', '반도체']</t>
+          <t>['주가', '거래정지', '분할상장']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10030</v>
+        <v>9940</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.96%</t>
+          <t>'-10.77%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F15" t="n">
         <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1800,13 +1800,13 @@
         <v>10880</v>
       </c>
       <c r="M15" t="n">
-        <v>9920</v>
+        <v>9890</v>
       </c>
       <c r="N15" t="n">
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>57744962575</v>
+        <v>59134326010</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>ESS 마진율 불확실성 및 투자 경고 등 하락세에 대한 우려.</t>
+          <t>주가 급락 및 투자경고 관련 우려. ESS 마진율 불확실성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['ESS', '마진율', '하락']</t>
+          <t>['주가', '투자경고', 'ESS']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_13.xlsx
+++ b/data/trending_integrated_20261022_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3755</v>
+        <v>3695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.52%</t>
+          <t>'+19.58%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G2" t="n">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>74365470879</v>
+        <v>77169918956</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -670,13 +670,13 @@
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F3" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G3" t="n">
-        <v>1316</v>
+        <v>1291</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>543067739850</v>
+        <v>547224655250</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 어닝 서프라이즈 및 자사주 취득 공시 발표. MSCI 편입 예상 등 긍정적 전망.</t>
+          <t>삼성E&amp;A, 시장 예상 상회하는 실적 발표와 자사주 취득 공시로 주가 상승 기대감 고조. MSCI 편입 및 공매도 청산 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '자사주 취득', 'MSCI 편입']</t>
+          <t>['어닝서프라이즈', '자사주 취득', 'MSCI 편입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7360</v>
+        <v>7340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.51%</t>
+          <t>'+10.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8873847110</v>
+        <v>8912303620</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>1675</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+4.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>21769051185</v>
+        <v>22061437269</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 및 주가 조작 의혹 제기. 특정 가격 도달 기대감.</t>
+          <t>푸드나무, 주가 조작 의혹 및 보호예수 해제 물량에 대한 우려. 일부 긍정적 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수', '주가조작', '매물벽']</t>
+          <t>['주가 조작', '보호예수', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14690</v>
+        <v>1715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.54%</t>
+          <t>'+3.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>246</v>
+        <v>119</v>
       </c>
       <c r="H6" t="n">
-        <v>9.949999999999999</v>
+        <v>5.01</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14770</v>
+        <v>1652</v>
       </c>
       <c r="K6" t="n">
-        <v>14770</v>
+        <v>1715</v>
       </c>
       <c r="L6" t="n">
-        <v>15290</v>
+        <v>1830</v>
       </c>
       <c r="M6" t="n">
-        <v>14610</v>
+        <v>1611</v>
       </c>
       <c r="N6" t="n">
-        <v>9.82</v>
+        <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>36174939375</v>
+        <v>27253132354</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>4980</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>735</v>
       </c>
       <c r="R6" t="n">
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="S6" t="n">
-        <v>-63000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인 및 연기금 순매수세 유입에도 건설주 전반의 낮은 상승률에 대한 불만 표출. 대차해지 운동 촉구.</t>
+          <t>앤로보틱스, 단기 급등 후 조정 국면. 일부 긍정적 전망과 함께 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 매수', '건설주', '대차해지']</t>
+          <t>['단기 급등', '변동성', '조정']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17790</v>
+        <v>17850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-0.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>87</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H7" t="n">
         <v>3.29</v>
@@ -1070,7 +1070,7 @@
         <v>3.61</v>
       </c>
       <c r="O7" t="n">
-        <v>72106167660</v>
+        <v>72486617340</v>
       </c>
       <c r="P7" t="n">
         <v>22450</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7250</v>
+        <v>14710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>587</v>
+        <v>248</v>
       </c>
       <c r="H8" t="n">
-        <v>25.47</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7350</v>
+        <v>14770</v>
       </c>
       <c r="K8" t="n">
-        <v>7270</v>
+        <v>14770</v>
       </c>
       <c r="L8" t="n">
-        <v>7340</v>
+        <v>15290</v>
       </c>
       <c r="M8" t="n">
-        <v>7120</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>25.45</v>
+        <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>13533498150</v>
+        <v>36722545990</v>
       </c>
       <c r="P8" t="n">
-        <v>17950</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>7120</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-148000</v>
+        <v>15000</v>
       </c>
       <c r="S8" t="n">
-        <v>-69000</v>
+        <v>-63000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>영업이익 및 순이익 흑자 발표 기반 주가 상승 기대. 30년 최저가 근접 상황.</t>
+          <t>외국인 및 연기금 순매수세 유입에도 건설주 전반의 낮은 상승률에 대한 불만 표출. 대차해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '순이익', '실적']</t>
+          <t>['외국인 매수', '건설주', '대차해지']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41300</v>
+        <v>7240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>810</v>
+        <v>626</v>
       </c>
       <c r="H9" t="n">
-        <v>13.09</v>
+        <v>25.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="K9" t="n">
-        <v>41850</v>
+        <v>7270</v>
       </c>
       <c r="L9" t="n">
-        <v>42350</v>
+        <v>7340</v>
       </c>
       <c r="M9" t="n">
-        <v>41150</v>
+        <v>7120</v>
       </c>
       <c r="N9" t="n">
-        <v>13.23</v>
+        <v>25.45</v>
       </c>
       <c r="O9" t="n">
-        <v>11512958250</v>
+        <v>13962342600</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>7120</v>
       </c>
       <c r="R9" t="n">
-        <v>46000</v>
+        <v>-148000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 속 기관 수급 확인. C2 결과 및 승인 가능성에 대한 논의.</t>
+          <t>LG디스플레이, 흑자 전환 및 순이익 증가에도 불구하고 주가 반응 미미. 장기간 누적된 적자와 낮은 주가에 대한 답답함 토로.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '간암', '승인']</t>
+          <t>['흑자 전환', '순이익', '주가 부진']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9900</v>
+        <v>9950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H10" t="n">
         <v>5.87</v>
@@ -1346,7 +1346,7 @@
         <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>15828221710</v>
+        <v>16255243605</v>
       </c>
       <c r="P10" t="n">
         <v>14940</v>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>213750</v>
+        <v>41300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F11" t="n">
-        <v>552</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>1617</v>
+        <v>816</v>
       </c>
       <c r="H11" t="n">
-        <v>46.14</v>
+        <v>13.09</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>223500</v>
+        <v>42350</v>
       </c>
       <c r="K11" t="n">
-        <v>221500</v>
+        <v>41850</v>
       </c>
       <c r="L11" t="n">
-        <v>226000</v>
+        <v>42350</v>
       </c>
       <c r="M11" t="n">
-        <v>213500</v>
+        <v>41150</v>
       </c>
       <c r="N11" t="n">
-        <v>46.08</v>
+        <v>13.23</v>
       </c>
       <c r="O11" t="n">
-        <v>1604236940250</v>
+        <v>11767824550</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-1004000</v>
+        <v>46000</v>
       </c>
       <c r="S11" t="n">
-        <v>-549000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 무관한 증시 부진에 대한 불만 표출. 개인 투자자들의 매도세 관찰.</t>
+          <t>HLB, 간암 치료제 FDA 승인 기대감 속에서 기관 매수세 확인. 결과 발표를 앞두고 신중론과 기대감이 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['증시', '매도세', '시스템']</t>
+          <t>['간암 치료제', 'FDA 승인', '기관 매수']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13590</v>
+        <v>215000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.03%</t>
+          <t>'-3.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>528</v>
       </c>
       <c r="G12" t="n">
-        <v>478</v>
+        <v>1548</v>
       </c>
       <c r="H12" t="n">
-        <v>3.48</v>
+        <v>46.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14310</v>
+        <v>223500</v>
       </c>
       <c r="K12" t="n">
-        <v>14180</v>
+        <v>221500</v>
       </c>
       <c r="L12" t="n">
-        <v>14830</v>
+        <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>13580</v>
+        <v>213500</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>102021081210</v>
+        <v>1657505081500</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1640</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-506000</v>
+        <v>-1004000</v>
       </c>
       <c r="S12" t="n">
-        <v>-3000</v>
+        <v>-549000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스. 삼성전자 인수 관련 루머.</t>
+          <t>삼성전자, 국내 증시 부진 및 정치적 이슈와 연관된 부정적 언급 다수. 실적 호재에도 불구하고 시장 전반의 하락세 영향.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['EUV', '유리기판', 'AI광통신']</t>
+          <t>['국내 증시', '정치적 이슈', '시장 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14140</v>
+        <v>13560</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.61%</t>
+          <t>'-5.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>0.33</v>
       </c>
       <c r="E13" t="n">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>186</v>
+        <v>482</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>3.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>14310</v>
       </c>
       <c r="K13" t="n">
-        <v>14460</v>
+        <v>14180</v>
       </c>
       <c r="L13" t="n">
-        <v>16140</v>
+        <v>14830</v>
       </c>
       <c r="M13" t="n">
-        <v>13550</v>
+        <v>13500</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>78734290330</v>
+        <v>106814190335</v>
       </c>
       <c r="P13" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>12030</v>
+        <v>1640</v>
       </c>
       <c r="R13" t="n">
-        <v>-51000</v>
+        <v>-506000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
+          <t>대한광통신, EUV용 유리기판 제조 기술 확보 소식에 따른 기대감. AI 광통신 관련 뉴스와 함께 주가 흐름에 대한 다양한 의견.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '보호예수']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1207500</v>
+        <v>14110</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.68%</t>
+          <t>'-5.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="F14" t="n">
-        <v>543</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>1513</v>
+        <v>194</v>
       </c>
       <c r="H14" t="n">
-        <v>48.79</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1294000</v>
+        <v>14980</v>
       </c>
       <c r="K14" t="n">
-        <v>1273000</v>
+        <v>14460</v>
       </c>
       <c r="L14" t="n">
-        <v>1297000</v>
+        <v>16140</v>
       </c>
       <c r="M14" t="n">
-        <v>1204000</v>
+        <v>13550</v>
       </c>
       <c r="N14" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2091217386000</v>
+        <v>79067796945</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q14" t="n">
-        <v>468000</v>
+        <v>12030</v>
       </c>
       <c r="R14" t="n">
-        <v>-62000</v>
+        <v>-51000</v>
       </c>
       <c r="S14" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급 및 주가 부진에 대한 불만. 거래 정지 및 분할 상장 관련 언급.</t>
+          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가', '거래정지', '분할상장']</t>
+          <t>['반도체', 'AI', '보호예수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,97 +1752,189 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9940</v>
+        <v>1218000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-10.77%</t>
+          <t>'-5.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.41</v>
+        <v>0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>176</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>554</v>
       </c>
       <c r="G15" t="n">
-        <v>469</v>
+        <v>1609</v>
       </c>
       <c r="H15" t="n">
-        <v>3.69</v>
+        <v>48.79</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>11140</v>
+        <v>1294000</v>
       </c>
       <c r="K15" t="n">
-        <v>10830</v>
+        <v>1273000</v>
       </c>
       <c r="L15" t="n">
-        <v>10880</v>
+        <v>1297000</v>
       </c>
       <c r="M15" t="n">
-        <v>9890</v>
+        <v>1204000</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>48.77</v>
       </c>
       <c r="O15" t="n">
-        <v>59134326010</v>
+        <v>2199980411000</v>
       </c>
       <c r="P15" t="n">
-        <v>11690</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>2270</v>
+        <v>468000</v>
       </c>
       <c r="R15" t="n">
-        <v>-205000</v>
+        <v>-62000</v>
       </c>
       <c r="S15" t="n">
-        <v>12000</v>
+        <v>-88000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 급락 및 투자경고 관련 우려. ESS 마진율 불확실성 언급.</t>
+          <t>SK하이닉스, 정치적 발언 및 특정 지역 관련 부정적 언급 위주. 주가 하락에 대한 불만과 정치적 이슈에 대한 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['정치적 발언', '주가 하락', '지역 비하']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10030</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-9.96%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E16" t="n">
+        <v>178</v>
+      </c>
+      <c r="F16" t="n">
+        <v>88</v>
+      </c>
+      <c r="G16" t="n">
+        <v>477</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>11140</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10830</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10880</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9890</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>59719655790</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-205000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>HT로보틱스, 급락 및 투기 과열 종목 지정에 따른 우려. 향후 주가 전망에 대한 부정적 의견 지배적.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
         <v>0.1</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>['주가', '투자경고', 'ESS']</t>
-        </is>
-      </c>
-      <c r="X15" t="n">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['급락', '투기 과열', '신용 비율']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
         <v>5</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>396300</t>
         </is>
